--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -8456,44 +8456,57 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="inlineStr">
-        <is>
-          <t>Coffee Studio 7gr.</t>
-        </is>
-      </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>Corso Venezia, 31</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>02/38238682</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr"/>
-      <c r="E135" s="1" t="inlineStr"/>
-      <c r="F135" s="1" t="inlineStr"/>
-      <c r="G135" s="1" t="inlineStr"/>
-      <c r="H135" s="1" t="inlineStr"/>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr"/>
-      <c r="K135" s="1" t="inlineStr"/>
-      <c r="L135" s="1" t="inlineStr"/>
-      <c r="M135" s="1" t="inlineStr"/>
-      <c r="N135" s="1" t="inlineStr"/>
-      <c r="O135" s="1" t="inlineStr"/>
-      <c r="P135" s="1" t="inlineStr"/>
-      <c r="Q135" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R135" s="1" t="inlineStr">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Pasticceria Passerini dal 1919</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Via Victor Hugo, 4</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>02/8693614</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>www.passerinilecco.it</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>pasticceriapasserini</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Rating Google: 3.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (pasticceriapasserini)</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
@@ -8502,32 +8515,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Pasticceria Passerini dal 1919</t>
+          <t>Brylla</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Via Victor Hugo, 4</t>
+          <t>Via Giovanni Rasori, 12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>02/8693614</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>www.passerinilecco.it</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>pasticceriapasserini</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>02/64089167</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8540,14 +8538,14 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '17', 'closes': '22'}, 'martedì': {'opens': '17', 'closes':</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Rating Google: 3.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (pasticceriapasserini)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -8559,17 +8557,42 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Brylla</t>
+          <t>Cantine Isola</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Via Giovanni Rasori, 12</t>
+          <t>Via Paolo Sarpi, 30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>02/64089167</t>
+          <t>02/3315249</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>www.cantineisola.com</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>cantineisola</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>cantine_isola</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8577,19 +8600,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '17', 'closes': '22'}, 'martedì': {'opens': '17', 'closes':</t>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (cantineisola) | IG: trovato (cantine_isola)</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -8601,32 +8619,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cantine Isola</t>
+          <t>Ceresio 7</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Via Paolo Sarpi, 30</t>
+          <t>Via Ceresio, 7</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>02/3315249</t>
+          <t>02/31039221</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>www.cantineisola.com</t>
+          <t>www.ceresio7.com</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>cantineisola</t>
+          <t>ceresio7</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>cantine_isola</t>
+          <t>ceresio7</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8644,6 +8662,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30', 'closes': '01'}, 'martedì': {'opens': '12:30', 'cl</t>
+        </is>
+      </c>
       <c r="O138" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8651,7 +8679,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (cantineisola) | IG: trovato (cantine_isola)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (ceresio7) | IG: trovato (ceresio7)</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -8663,32 +8691,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ceresio 7</t>
+          <t>Cru</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Via Ceresio, 7</t>
+          <t>Piazza Sempione, 6</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>02/31039221</t>
+          <t>342/3040081</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>www.ceresio7.com</t>
+          <t>www.crumilano.com</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ceresio7</t>
+          <t>crumilanowinebar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ceresio7</t>
+          <t>cru_milano</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8713,7 +8741,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12:30', 'closes': '01'}, 'martedì': {'opens': '12:30', 'cl</t>
+          <t>{'lunedì': {'opens': '18', 'closes': '01'}, 'martedì': {'opens': '18', 'closes':</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -8723,7 +8751,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (ceresio7) | IG: trovato (ceresio7)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (crumilanowinebar) | IG: trovato (cru_milano)</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -8735,32 +8763,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Cru</t>
+          <t>Enoteca Naturale</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Piazza Sempione, 6</t>
+          <t>Via Santa Croce, 19/A</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>342/3040081</t>
+          <t>02/82770589</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>www.crumilano.com</t>
+          <t>www.enotecanaturale.it</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>crumilanowinebar</t>
+          <t>enotecanaturale</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>cru_milano</t>
+          <t>enotecanaturale</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8778,16 +8806,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '01'}, 'martedì': {'opens': '18', 'closes':</t>
-        </is>
-      </c>
       <c r="O140" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8795,7 +8813,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (crumilanowinebar) | IG: trovato (cru_milano)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (enotecanaturale) | IG: trovato (enotecanaturale)</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -8807,32 +8825,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Enoteca Naturale</t>
+          <t>Flor. | born to be wine</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Via Santa Croce, 19/A</t>
+          <t>Via Vigevano, 6</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>02/82770589</t>
+          <t>340/8587572</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>www.enotecanaturale.it</t>
+          <t>www.florwine.com</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>enotecanaturale</t>
+          <t>milanoflor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>enotecanaturale</t>
+          <t>florenoteca.milano</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8850,6 +8868,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '23:30'}, 'martedì': {'opens': '18', 'close</t>
+        </is>
+      </c>
       <c r="O141" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8857,7 +8885,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (enotecanaturale) | IG: trovato (enotecanaturale)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (milanoflor) | IG: trovato (florenoteca.milano)</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -8869,32 +8897,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Flor. | born to be wine</t>
+          <t>Mesté - vino e fornelli</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Via Vigevano, 6</t>
+          <t>Via Corrado II il Salico, 12</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>340/8587572</t>
+          <t>346/8061538</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>www.florwine.com</t>
+          <t>www.meste.it</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>milanoflor</t>
+          <t>mestemilano</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>florenoteca.milano</t>
+          <t>mestemilano</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8919,7 +8947,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '23:30'}, 'martedì': {'opens': '18', 'close</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 18:30', 'closes': '</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -8929,7 +8957,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (milanoflor) | IG: trovato (florenoteca.milano)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (mestemilano) | IG: trovato (mestemilano)</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -8941,42 +8969,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mesté - vino e fornelli</t>
+          <t>Millésime 1990 - sorsi di Francia</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Via Corrado II il Salico, 12</t>
+          <t>Via Raffaello Sanzio, 4</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>346/8061538</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>www.meste.it</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>mestemilano</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>mestemilano</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>02/36534945</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8989,19 +8992,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 18:30', 'closes': '</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (mestemilano) | IG: trovato (mestemilano)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -9013,17 +9006,42 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Millésime 1990 - sorsi di Francia</t>
+          <t>Nik’s &amp; Co</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Via Raffaello Sanzio, 4</t>
+          <t>Via Giovanni Schiaparelli, 14</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>02/36534945</t>
+          <t>02/91571797</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>www.niksandco.it</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>niksandco</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>niks_co</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9036,9 +9054,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (niksandco) | IG: trovato (niks_co)</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -9050,42 +9073,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Nik’s &amp; Co</t>
+          <t>Shiua</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Via Giovanni Schiaparelli, 14</t>
+          <t>Via Solari, 43</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>02/91571797</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>www.niksandco.it</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>niksandco</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>niks_co</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>01/02/2026</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>345/0229180</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9098,14 +9096,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (niksandco) | IG: trovato (niks_co)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -9117,17 +9110,42 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Shiua</t>
+          <t>Tipografia Alimentare</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Via Solari, 43</t>
+          <t>Via Dolomiti, 1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>345/0229180</t>
+          <t>02/83537868</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>www.tipografiaalimentare.it</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>tipografiaalimentare</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>tipografiaalimentare</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9140,9 +9158,19 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '23'}, 'martedì': {'opens': 'Chiuso'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: trovato (tipografiaalimentare) | IG: trovato (tipografiaalimentare)</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -9154,37 +9182,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Tipografia Alimentare</t>
+          <t>Vineria Eretica</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Via Dolomiti, 1</t>
+          <t>Via Rosolino Pilo, 14</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>02/83537868</t>
+          <t>02/45942171</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>www.tipografiaalimentare.it</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>tipografiaalimentare</t>
+          <t>www.vineriaeretica.it</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>tipografiaalimentare</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>vineriaeretica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9204,7 +9222,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12', 'closes': '23'}, 'martedì': {'opens': 'Chiuso'}, 'mer</t>
+          <t>{'lunedì': {'opens': '18', 'closes': '23:30'}, 'martedì': {'opens': '18', 'close</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -9214,7 +9232,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: trovato (tipografiaalimentare) | IG: trovato (tipografiaalimentare)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (vineriaeretica)</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -9226,32 +9244,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Vineria Eretica</t>
+          <t>Vinodromo</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Via Rosolino Pilo, 14</t>
+          <t>Via Salasco, 21</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>02/45942171</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>www.vineriaeretica.it</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>vineriaeretica</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>02/32960708</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9266,17 +9269,12 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '23:30'}, 'martedì': {'opens': '18', 'close</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (vineriaeretica)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -9288,17 +9286,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Vinodromo</t>
+          <t>Wineria</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Via Salasco, 21</t>
+          <t>Piazza Carlo Caneva, 4</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>02/32960708</t>
+          <t>02/39464196</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9313,7 +9311,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
+          <t>{'lunedì': {'opens': '15', 'closes': '22'}, 'martedì': {'opens': '11', 'closes':</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -9330,17 +9328,42 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Wineria</t>
+          <t>Osteria alla Concorrenza</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Piazza Carlo Caneva, 4</t>
+          <t>Via Melzo, 12</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>02/39464196</t>
+          <t>02/91672012</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>www.osteriaallaconcorrenza.superbexperience.com</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>osteriaallaconcorrenza</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>osteria_alla_concorrenza</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9355,12 +9378,17 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '15', 'closes': '22'}, 'martedì': {'opens': '11', 'closes':</t>
+          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (osteriaallaconcorrenza) | IG: trovato (osteria_alla_concorrenza)</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -9370,44 +9398,62 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="inlineStr">
-        <is>
-          <t>Barba</t>
-        </is>
-      </c>
-      <c r="B151" s="1" t="inlineStr">
-        <is>
-          <t>Via San Gregorio, 40</t>
-        </is>
-      </c>
-      <c r="C151" s="1" t="inlineStr">
-        <is>
-          <t>02/36515846</t>
-        </is>
-      </c>
-      <c r="D151" s="1" t="inlineStr"/>
-      <c r="E151" s="1" t="inlineStr"/>
-      <c r="F151" s="1" t="inlineStr"/>
-      <c r="G151" s="1" t="inlineStr"/>
-      <c r="H151" s="1" t="inlineStr"/>
-      <c r="I151" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J151" s="1" t="inlineStr"/>
-      <c r="K151" s="1" t="inlineStr"/>
-      <c r="L151" s="1" t="inlineStr"/>
-      <c r="M151" s="1" t="inlineStr"/>
-      <c r="N151" s="1" t="inlineStr"/>
-      <c r="O151" s="1" t="inlineStr"/>
-      <c r="P151" s="1" t="inlineStr"/>
-      <c r="Q151" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R151" s="1" t="inlineStr">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Palinurobar</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Via Giovanni Paisello, 28</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>www.palinurobar.it</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>palinurobar</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '17:45', 'closes': '00'}, 'martedì': {'opens': '17:45', 'cl</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (palinurobar)</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
@@ -9416,42 +9462,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Osteria alla Concorrenza</t>
+          <t>Porcobrado</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Via Melzo, 12</t>
+          <t>Via Jacopo dal Verme, 17</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>02/91672012</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>www.osteriaallaconcorrenza.superbexperience.com</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>osteriaallaconcorrenza</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>osteria_alla_concorrenza</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>02/87030181 - 338/3339120</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9466,17 +9487,12 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (osteriaallaconcorrenza) | IG: trovato (osteria_alla_concorrenza)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -9488,27 +9504,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Palinurobar</t>
+          <t>Silvano - vini e cibi al banco</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Via Giovanni Paisello, 28</t>
+          <t>Piazza Morbegno, 2</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>n.d.</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>www.palinurobar.it</t>
+          <t>02/72193827</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>palinurobar</t>
+          <t>silvano_viniecibi</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9528,7 +9539,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '17:45', 'closes': '00'}, 'martedì': {'opens': '17:45', 'cl</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -9538,7 +9549,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (palinurobar)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (silvano_viniecibi)</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -9550,17 +9561,32 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Porcobrado</t>
+          <t>Temp enoteca</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Via Jacopo dal Verme, 17</t>
+          <t>Via Pasquale Sottocorno, 17</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>02/87030181 - 338/3339120</t>
+          <t>347/2402269</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>www.tempenoteca.it</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>temp.enoteca</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9575,12 +9601,17 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
+          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (temp.enoteca)</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -9592,22 +9623,37 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Silvano - vini e cibi al banco</t>
+          <t>Kilburn</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Piazza Morbegno, 2</t>
+          <t>Via Panfilo Castaldi, 35</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>02/72193827</t>
+          <t>02/36580751</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>www.kilburncocktailbarmilano.it</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>KilburnMilano</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>silvano_viniecibi</t>
+          <t>kilburn_milano</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9627,7 +9673,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
+          <t>{'lunedì': {'opens': '19', 'closes': '00'}, 'martedì': {'opens': '19', 'closes':</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -9637,7 +9683,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (silvano_viniecibi)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (KilburnMilano) | IG: trovato (kilburn_milano)</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -9649,27 +9695,37 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Temp enoteca</t>
+          <t>Lacerba</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Via Pasquale Sottocorno, 17</t>
+          <t>Via Orti, 4</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>347/2402269</t>
+          <t>02/ 545 5475</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>www.tempenoteca.it</t>
+          <t>www.lacerba.it</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>lacerba.milano</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>temp.enoteca</t>
+          <t>lacerba.milano</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9687,11 +9743,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
-        </is>
-      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>Si</t>
@@ -9699,7 +9750,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (temp.enoteca)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (lacerba.milano) | IG: trovato (lacerba.milano)</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -9711,32 +9762,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Kilburn</t>
+          <t>Mag cafè</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Via Panfilo Castaldi, 35</t>
+          <t>Ripa di Porta Ticinese, 3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>02/36580751</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>www.kilburncocktailbarmilano.it</t>
+          <t>02/39562875</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>KilburnMilano</t>
+          <t>magcafemilano</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>kilburn_milano</t>
+          <t>magcafe</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9761,7 +9807,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '19', 'closes': '00'}, 'martedì': {'opens': '19', 'closes':</t>
+          <t>{'lunedì': {'opens': '08', 'closes': '02'}, 'martedì': {'opens': '08', 'closes':</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -9771,7 +9817,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (KilburnMilano) | IG: trovato (kilburn_milano)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (magcafemilano) | IG: trovato (magcafe)</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -9783,32 +9829,27 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Lacerba</t>
+          <t>Norah was drunk</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Via Orti, 4</t>
+          <t>Via Nicola Antonio Porpora, 169</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>02/ 545 5475</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>www.lacerba.it</t>
+          <t>02/83428246 - 375/7746998</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>lacerba.milano</t>
+          <t>norahwasdrunk</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>lacerba.milano</t>
+          <t>norah_milano</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9831,6 +9872,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '02'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
       <c r="O158" t="inlineStr">
         <is>
           <t>Si</t>
@@ -9838,7 +9884,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (lacerba.milano) | IG: trovato (lacerba.milano)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (norahwasdrunk) | IG: trovato (norah_milano)</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -9850,27 +9896,32 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Mag cafè</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ripa di Porta Ticinese, 3</t>
+          <t>Via Angelo Fumagalli, 1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>02/39562875</t>
+          <t>02/8372865</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>www.ritacocktails.com</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>magcafemilano</t>
+          <t>RitaCocktails</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>magcafe</t>
+          <t>ritacocktails</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9888,16 +9939,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '08', 'closes': '02'}, 'martedì': {'opens': '08', 'closes':</t>
-        </is>
-      </c>
       <c r="O159" t="inlineStr">
         <is>
           <t>Si</t>
@@ -9905,7 +9946,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (magcafemilano) | IG: trovato (magcafe)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (RitaCocktails) | IG: trovato (ritacocktails)</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -9917,37 +9958,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Norah was drunk</t>
+          <t>Scott Bar</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Via Nicola Antonio Porpora, 169</t>
+          <t>Viale Bianca Maria, 4</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>02/83428246 - 375/7746998</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>norahwasdrunk</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>norah_milano</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>02/00244399</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9962,17 +9983,12 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '02'}, 'martedì': {'opens': '18', 'closes':</t>
-        </is>
-      </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '12, 17', 'closes': '14:30, 01', 'break': '14:30–17'}, 'mar</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (norahwasdrunk) | IG: trovato (norah_milano)</t>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -9984,32 +10000,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>Tripstillery</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Via Angelo Fumagalli, 1</t>
+          <t>Piazza Alvar Aalto, snc</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>02/8372865</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>www.ritacocktails.com</t>
+          <t>02/62061443</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RitaCocktails</t>
+          <t>tripstillery</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ritacocktails</t>
+          <t>tripstillery</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -10034,7 +10045,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (RitaCocktails) | IG: trovato (ritacocktails)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (tripstillery) | IG: trovato (tripstillery)</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -10046,17 +10057,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Scott Bar</t>
+          <t>Bonci - pizza in teglia</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Viale Bianca Maria, 4</t>
+          <t>Via Nicola Piccinni, 3</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>02/00244399</t>
+          <t>340/8223165</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10071,12 +10082,12 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12, 17', 'closes': '14:30, 01', 'break': '14:30–17'}, 'mar</t>
+          <t>{'lunedì': {'opens': '11', 'closes': '21:30'}, 'martedì': {'opens': '11', 'close</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 3.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -10088,27 +10099,32 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Tripstillery</t>
+          <t>Carmen Gelato</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Piazza Alvar Aalto, snc</t>
+          <t>Via Carlo Ravizza, 3</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>02/62061443</t>
+          <t>02/84230543</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>www.carmengelato.com</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>tripstillery</t>
+          <t>carmengelato.ita</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>tripstillery</t>
+          <t>carmen_gelato</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -10126,6 +10142,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '13', 'closes': '22:30'}, 'martedì': {'opens': '13', 'close</t>
+        </is>
+      </c>
       <c r="O163" t="inlineStr">
         <is>
           <t>Si</t>
@@ -10133,7 +10159,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (tripstillery) | IG: trovato (tripstillery)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (carmengelato.ita) | IG: trovato (carmen_gelato)</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -10145,17 +10171,32 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Bonci - pizza in teglia</t>
+          <t>Ciacco</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Via Nicola Piccinni, 3</t>
+          <t>Via Spadari, 13</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>340/8223165</t>
+          <t>02/39663592</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>www.ciaccolab.it</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>ciaccogelato</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10170,12 +10211,17 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '11', 'closes': '21:30'}, 'martedì': {'opens': '11', 'close</t>
+          <t>{'lunedì': {'opens': '12:30', 'closes': '15:30'}, 'martedì': {'opens': '12:30, 1</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>Rating Google: 3.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (ciaccogelato) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -10187,32 +10233,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Carmen Gelato</t>
+          <t>Gelateria LatteNeve</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Via Carlo Ravizza, 3</t>
+          <t>Via Vigevano, 27</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>02/84230543</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>www.carmengelato.com</t>
+          <t>02/39811258</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>carmengelato.ita</t>
+          <t>lattenevemilano</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>carmen_gelato</t>
+          <t>latteneve</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -10237,7 +10278,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '13', 'closes': '22:30'}, 'martedì': {'opens': '13', 'close</t>
+          <t>{'lunedì': {'opens': '12:45', 'closes': '22'}, 'martedì': {'opens': '12:45', 'cl</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -10247,7 +10288,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (carmengelato.ita) | IG: trovato (carmen_gelato)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (lattenevemilano) | IG: trovato (latteneve)</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -10259,27 +10300,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ciacco</t>
+          <t>Gelateria Paganelli</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Via Spadari, 13</t>
+          <t>Via Adda, 3</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>02/39663592</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>www.ciaccolab.it</t>
+          <t>02/42441183</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ciaccogelato</t>
+          <t>gelateriapaganelli</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>gelateriapaganelli</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10287,6 +10328,11 @@
           <t>N/D</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I166" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -10299,7 +10345,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12:30', 'closes': '15:30'}, 'martedì': {'opens': '12:30, 1</t>
+          <t>{'lunedì': {'opens': '11:30', 'closes': '21:30'}, 'martedì': {'opens': '11:30',</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -10309,7 +10355,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (ciaccogelato) | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (gelateriapaganelli) | IG: trovato (gelateriapaganelli)</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -10321,27 +10367,32 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Gelateria LatteNeve</t>
+          <t>Gelateria Prossima Fermata</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Via Vigevano, 27</t>
+          <t>Via Melchiorre Gioia, 131</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>02/39811258</t>
+          <t>333/3112637</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>www.gelateria.company.site</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>lattenevemilano</t>
+          <t>gelateria.Prossima.Fermata</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>latteneve</t>
+          <t>gelateria.prossima.fermata</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10359,602 +10410,596 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gelateria.Prossima.Fermata) | IG: trovato (gelateria.prossima.fermata)</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>Coffee Studio 7gr.</t>
+        </is>
+      </c>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>Corso Venezia, 31</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>02/38238682</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="inlineStr"/>
+      <c r="E168" s="1" t="inlineStr"/>
+      <c r="F168" s="1" t="inlineStr"/>
+      <c r="G168" s="1" t="inlineStr"/>
+      <c r="H168" s="1" t="inlineStr"/>
+      <c r="I168" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J168" s="1" t="inlineStr"/>
+      <c r="K168" s="1" t="inlineStr"/>
+      <c r="L168" s="1" t="inlineStr"/>
+      <c r="M168" s="1" t="inlineStr"/>
+      <c r="N168" s="1" t="inlineStr"/>
+      <c r="O168" s="1" t="inlineStr"/>
+      <c r="P168" s="1" t="inlineStr"/>
+      <c r="Q168" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R168" s="1" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>Via San Gregorio, 40</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>02/36515846</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="inlineStr"/>
+      <c r="E169" s="1" t="inlineStr"/>
+      <c r="F169" s="1" t="inlineStr"/>
+      <c r="G169" s="1" t="inlineStr"/>
+      <c r="H169" s="1" t="inlineStr"/>
+      <c r="I169" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J169" s="1" t="inlineStr"/>
+      <c r="K169" s="1" t="inlineStr"/>
+      <c r="L169" s="1" t="inlineStr"/>
+      <c r="M169" s="1" t="inlineStr"/>
+      <c r="N169" s="1" t="inlineStr"/>
+      <c r="O169" s="1" t="inlineStr"/>
+      <c r="P169" s="1" t="inlineStr"/>
+      <c r="Q169" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R169" s="1" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Gelato Giusto</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Via San Gregorio, 17</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>02/29510284</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>www.gelatogiusto.it</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>gelatogiustomi</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>gelatogiusto</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '12:45', 'closes': '22'}, 'martedì': {'opens': '12:45', 'cl</t>
-        </is>
-      </c>
-      <c r="O167" t="inlineStr">
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '23'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (lattenevemilano) | IG: trovato (latteneve)</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Gelateria Paganelli</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Via Adda, 3</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>02/42441183</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>gelateriapaganelli</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>gelateriapaganelli</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (gelatogiustomi) | IG: trovato (gelatogiusto)</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>GnomoGelato</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Via Francesco Cherubini, 3</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>02/4818134</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>www.lognomogelato.it</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>gnomogelato</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>gnomogelato</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '11:30', 'closes': '21:30'}, 'martedì': {'opens': '11:30',</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '23'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (gelateriapaganelli) | IG: trovato (gelateriapaganelli)</t>
-        </is>
-      </c>
-      <c r="R168" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Gelateria Prossima Fermata</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Via Melchiorre Gioia, 131</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>333/3112637</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>www.gelateria.company.site</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>gelateria.Prossima.Fermata</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>gelateria.prossima.fermata</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (gnomogelato) | IG: trovato (gnomogelato)</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Gusto 17</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Via Savona, 17</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>02/39811835</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>www.gusto17.com</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>gusto17ilgelato</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>gusto17_ilgelato</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gelateria.Prossima.Fermata) | IG: trovato (gelateria.prossima.fermata)</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="1" t="inlineStr">
-        <is>
-          <t>Gelato Giusto</t>
-        </is>
-      </c>
-      <c r="B170" s="1" t="inlineStr">
-        <is>
-          <t>Via San Gregorio, 17</t>
-        </is>
-      </c>
-      <c r="C170" s="1" t="inlineStr">
-        <is>
-          <t>02/29510284</t>
-        </is>
-      </c>
-      <c r="D170" s="1" t="inlineStr">
-        <is>
-          <t>www.gelatogiusto.it</t>
-        </is>
-      </c>
-      <c r="E170" s="1" t="inlineStr">
-        <is>
-          <t>gelatogiustomi</t>
-        </is>
-      </c>
-      <c r="F170" s="1" t="inlineStr">
-        <is>
-          <t>gelatogiusto</t>
-        </is>
-      </c>
-      <c r="G170" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H170" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I170" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J170" s="1" t="inlineStr"/>
-      <c r="K170" s="1" t="inlineStr"/>
-      <c r="L170" s="1" t="inlineStr"/>
-      <c r="M170" s="1" t="inlineStr"/>
-      <c r="N170" s="1" t="inlineStr"/>
-      <c r="O170" s="1" t="inlineStr"/>
-      <c r="P170" s="1" t="inlineStr"/>
-      <c r="Q170" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R170" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="1" t="inlineStr">
-        <is>
-          <t>GnomoGelato</t>
-        </is>
-      </c>
-      <c r="B171" s="1" t="inlineStr">
-        <is>
-          <t>Via Francesco Cherubini, 3</t>
-        </is>
-      </c>
-      <c r="C171" s="1" t="inlineStr">
-        <is>
-          <t>02/4818134</t>
-        </is>
-      </c>
-      <c r="D171" s="1" t="inlineStr">
-        <is>
-          <t>www.lognomogelato.it</t>
-        </is>
-      </c>
-      <c r="E171" s="1" t="inlineStr">
-        <is>
-          <t>gnomogelato</t>
-        </is>
-      </c>
-      <c r="F171" s="1" t="inlineStr">
-        <is>
-          <t>gnomogelato</t>
-        </is>
-      </c>
-      <c r="G171" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H171" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I171" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J171" s="1" t="inlineStr"/>
-      <c r="K171" s="1" t="inlineStr"/>
-      <c r="L171" s="1" t="inlineStr"/>
-      <c r="M171" s="1" t="inlineStr"/>
-      <c r="N171" s="1" t="inlineStr"/>
-      <c r="O171" s="1" t="inlineStr"/>
-      <c r="P171" s="1" t="inlineStr"/>
-      <c r="Q171" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R171" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="1" t="inlineStr">
-        <is>
-          <t>Gusto 17</t>
-        </is>
-      </c>
-      <c r="B172" s="1" t="inlineStr">
-        <is>
-          <t>Via Savona, 17</t>
-        </is>
-      </c>
-      <c r="C172" s="1" t="inlineStr">
-        <is>
-          <t>02/39811835</t>
-        </is>
-      </c>
-      <c r="D172" s="1" t="inlineStr">
-        <is>
-          <t>www.gusto17.com</t>
-        </is>
-      </c>
-      <c r="E172" s="1" t="inlineStr">
-        <is>
-          <t>gusto17ilgelato</t>
-        </is>
-      </c>
-      <c r="F172" s="1" t="inlineStr">
-        <is>
-          <t>gusto17_ilgelato</t>
-        </is>
-      </c>
-      <c r="G172" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H172" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I172" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J172" s="1" t="inlineStr"/>
-      <c r="K172" s="1" t="inlineStr"/>
-      <c r="L172" s="1" t="inlineStr"/>
-      <c r="M172" s="1" t="inlineStr"/>
-      <c r="N172" s="1" t="inlineStr"/>
-      <c r="O172" s="1" t="inlineStr"/>
-      <c r="P172" s="1" t="inlineStr"/>
-      <c r="Q172" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R172" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gusto17ilgelato) | IG: trovato (gusto17_ilgelato)</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="inlineStr">
+      <c r="A173" t="inlineStr">
         <is>
           <t>Il Massimo del Gelato</t>
         </is>
       </c>
-      <c r="B173" s="1" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Via Lodovico Castelvetro, 18</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>02/3494943</t>
         </is>
       </c>
-      <c r="D173" s="1" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>www.ilmassimodelgelato.it</t>
         </is>
       </c>
-      <c r="E173" s="1" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>ilmassimodelgelatomilano</t>
         </is>
       </c>
-      <c r="F173" s="1" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>massimodelgelato</t>
         </is>
       </c>
-      <c r="G173" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H173" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I173" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J173" s="1" t="inlineStr"/>
-      <c r="K173" s="1" t="inlineStr"/>
-      <c r="L173" s="1" t="inlineStr"/>
-      <c r="M173" s="1" t="inlineStr"/>
-      <c r="N173" s="1" t="inlineStr"/>
-      <c r="O173" s="1" t="inlineStr"/>
-      <c r="P173" s="1" t="inlineStr"/>
-      <c r="Q173" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R173" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '23'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (ilmassimodelgelatomilano) | IG: trovato (massimodelgelato)</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="inlineStr">
+      <c r="A174" t="inlineStr">
         <is>
           <t>La Bottega del Gelato Cardelli dal 1964</t>
         </is>
       </c>
-      <c r="B174" s="1" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Via Giovanni Battista Pergolesi, 3</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>02/2940 0076</t>
         </is>
       </c>
-      <c r="D174" s="1" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>www.labottegadelgelato.it</t>
         </is>
       </c>
-      <c r="E174" s="1" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>labottegadelgelatocardelli</t>
         </is>
       </c>
-      <c r="F174" s="1" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>labottegadelgelatocardelli</t>
         </is>
       </c>
-      <c r="G174" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H174" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I174" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J174" s="1" t="inlineStr"/>
-      <c r="K174" s="1" t="inlineStr"/>
-      <c r="L174" s="1" t="inlineStr"/>
-      <c r="M174" s="1" t="inlineStr"/>
-      <c r="N174" s="1" t="inlineStr"/>
-      <c r="O174" s="1" t="inlineStr"/>
-      <c r="P174" s="1" t="inlineStr"/>
-      <c r="Q174" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R174" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '10:30', 'closes': '23'}, 'venerdì': {'opens': '10:30', 'c</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (labottegadelgelatocardelli) | IG: trovato (labottegadelgelatocardelli)</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="inlineStr">
+      <c r="A175" t="inlineStr">
         <is>
           <t>La Gelateria della Musica</t>
         </is>
       </c>
-      <c r="B175" s="1" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Via Lodovico il Moro, 3</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>02/39288619</t>
         </is>
       </c>
-      <c r="D175" s="1" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>www.lagelateriadellamusica.it</t>
         </is>
       </c>
-      <c r="E175" s="1" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>lagelateriadellamusica</t>
         </is>
       </c>
-      <c r="F175" s="1" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>lagelateriadellamusica</t>
         </is>
       </c>
-      <c r="G175" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H175" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I175" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J175" s="1" t="inlineStr"/>
-      <c r="K175" s="1" t="inlineStr"/>
-      <c r="L175" s="1" t="inlineStr"/>
-      <c r="M175" s="1" t="inlineStr"/>
-      <c r="N175" s="1" t="inlineStr"/>
-      <c r="O175" s="1" t="inlineStr"/>
-      <c r="P175" s="1" t="inlineStr"/>
-      <c r="Q175" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R175" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '13:30', 'closes': '22:30'}, 'venerdì': {'opens': '13:30',</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (lagelateriadellamusica) | IG: trovato (lagelateriadellamusica)</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="inlineStr">
+      <c r="A176" t="inlineStr">
         <is>
           <t>Macelleria Popolare</t>
         </is>
       </c>
-      <c r="B176" s="1" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Piazza XXIV Maggio - Mercato Coperto</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>02/39468368</t>
         </is>
       </c>
-      <c r="D176" s="1" t="inlineStr"/>
-      <c r="E176" s="1" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>mangiaridistradaalmercato</t>
         </is>
       </c>
-      <c r="F176" s="1" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>noi_della_macelleriapopolare</t>
         </is>
       </c>
-      <c r="G176" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H176" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I176" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J176" s="1" t="inlineStr"/>
-      <c r="K176" s="1" t="inlineStr"/>
-      <c r="L176" s="1" t="inlineStr"/>
-      <c r="M176" s="1" t="inlineStr"/>
-      <c r="N176" s="1" t="inlineStr"/>
-      <c r="O176" s="1" t="inlineStr"/>
-      <c r="P176" s="1" t="inlineStr"/>
-      <c r="Q176" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R176" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '10', 'closes': '21:30'}, 'venerdì': {'opens': '10', 'clos</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (mangiaridistradaalmercato) | IG: trovato (noi_della_macelleriapopolare)</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -10993,408 +11038,401 @@
       <c r="P177" s="1" t="inlineStr"/>
       <c r="Q177" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="inlineStr">
+      <c r="A178" t="inlineStr">
         <is>
           <t>Out of the Box</t>
         </is>
       </c>
-      <c r="B178" s="1" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Via Marcello Malpighi, 7</t>
         </is>
       </c>
-      <c r="C178" s="1" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>02/36637300</t>
         </is>
       </c>
-      <c r="D178" s="1" t="inlineStr"/>
-      <c r="E178" s="1" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>outofthebox.gelato</t>
         </is>
       </c>
-      <c r="F178" s="1" t="inlineStr"/>
-      <c r="G178" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H178" s="1" t="inlineStr"/>
-      <c r="I178" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J178" s="1" t="inlineStr"/>
-      <c r="K178" s="1" t="inlineStr"/>
-      <c r="L178" s="1" t="inlineStr"/>
-      <c r="M178" s="1" t="inlineStr"/>
-      <c r="N178" s="1" t="inlineStr"/>
-      <c r="O178" s="1" t="inlineStr"/>
-      <c r="P178" s="1" t="inlineStr"/>
-      <c r="Q178" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R178" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '00'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (outofthebox.gelato) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="inlineStr">
+      <c r="A179" t="inlineStr">
         <is>
           <t>Pantera Pizza Rustica</t>
         </is>
       </c>
-      <c r="B179" s="1" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Piazza XXIV Maggio - Mercato Coperto</t>
         </is>
       </c>
-      <c r="C179" s="1" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>n.d.</t>
         </is>
       </c>
-      <c r="D179" s="1" t="inlineStr"/>
-      <c r="E179" s="1" t="inlineStr"/>
-      <c r="F179" s="1" t="inlineStr"/>
-      <c r="G179" s="1" t="inlineStr"/>
-      <c r="H179" s="1" t="inlineStr"/>
-      <c r="I179" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J179" s="1" t="inlineStr"/>
-      <c r="K179" s="1" t="inlineStr"/>
-      <c r="L179" s="1" t="inlineStr"/>
-      <c r="M179" s="1" t="inlineStr"/>
-      <c r="N179" s="1" t="inlineStr"/>
-      <c r="O179" s="1" t="inlineStr"/>
-      <c r="P179" s="1" t="inlineStr"/>
-      <c r="Q179" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R179" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="inlineStr">
+      <c r="A180" t="inlineStr">
         <is>
           <t>Pavè Gelati&amp;Granite</t>
         </is>
       </c>
-      <c r="B180" s="1" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Via Cesare Battisti, 21</t>
         </is>
       </c>
-      <c r="C180" s="1" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>02/94383619</t>
         </is>
       </c>
-      <c r="D180" s="1" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>www.pavemilano.com</t>
         </is>
       </c>
-      <c r="E180" s="1" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>pavemilano</t>
         </is>
       </c>
-      <c r="F180" s="1" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>pavemilano</t>
         </is>
       </c>
-      <c r="G180" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H180" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I180" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J180" s="1" t="inlineStr"/>
-      <c r="K180" s="1" t="inlineStr"/>
-      <c r="L180" s="1" t="inlineStr"/>
-      <c r="M180" s="1" t="inlineStr"/>
-      <c r="N180" s="1" t="inlineStr"/>
-      <c r="O180" s="1" t="inlineStr"/>
-      <c r="P180" s="1" t="inlineStr"/>
-      <c r="Q180" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R180" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (pavemilano) | IG: trovato (pavemilano)</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="inlineStr">
+      <c r="A181" t="inlineStr">
         <is>
           <t>Rigoletto</t>
         </is>
       </c>
-      <c r="B181" s="1" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Via Cola di Rienzo, 2</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>02/38239075</t>
         </is>
       </c>
-      <c r="D181" s="1" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>www.gelateriarigoletto.it</t>
         </is>
       </c>
-      <c r="E181" s="1" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>gelateriarigoletto.it</t>
         </is>
       </c>
-      <c r="F181" s="1" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>gelateriarigoletto</t>
         </is>
       </c>
-      <c r="G181" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H181" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I181" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J181" s="1" t="inlineStr"/>
-      <c r="K181" s="1" t="inlineStr"/>
-      <c r="L181" s="1" t="inlineStr"/>
-      <c r="M181" s="1" t="inlineStr"/>
-      <c r="N181" s="1" t="inlineStr"/>
-      <c r="O181" s="1" t="inlineStr"/>
-      <c r="P181" s="1" t="inlineStr"/>
-      <c r="Q181" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R181" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (gelateriarigoletto.it) | IG: trovato (gelateriarigoletto)</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="inlineStr">
+      <c r="A182" t="inlineStr">
         <is>
           <t>Terra Gelato</t>
         </is>
       </c>
-      <c r="B182" s="1" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Via Vitruvio, 38</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>02/91948458</t>
         </is>
       </c>
-      <c r="D182" s="1" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>www.terragelato.it</t>
         </is>
       </c>
-      <c r="E182" s="1" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>TerraGelato</t>
         </is>
       </c>
-      <c r="F182" s="1" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>terragelato</t>
         </is>
       </c>
-      <c r="G182" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H182" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I182" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J182" s="1" t="inlineStr"/>
-      <c r="K182" s="1" t="inlineStr"/>
-      <c r="L182" s="1" t="inlineStr"/>
-      <c r="M182" s="1" t="inlineStr"/>
-      <c r="N182" s="1" t="inlineStr"/>
-      <c r="O182" s="1" t="inlineStr"/>
-      <c r="P182" s="1" t="inlineStr"/>
-      <c r="Q182" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R182" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (TerraGelato) | IG: trovato (terragelato)</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="inlineStr">
+      <c r="A183" t="inlineStr">
         <is>
           <t>Tra le righe Gelato &amp; Friends</t>
         </is>
       </c>
-      <c r="B183" s="1" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Via Teodosio, 44</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>02/91762549</t>
         </is>
       </c>
-      <c r="D183" s="1" t="inlineStr"/>
-      <c r="E183" s="1" t="inlineStr"/>
-      <c r="F183" s="1" t="inlineStr"/>
-      <c r="G183" s="1" t="inlineStr"/>
-      <c r="H183" s="1" t="inlineStr"/>
-      <c r="I183" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J183" s="1" t="inlineStr"/>
-      <c r="K183" s="1" t="inlineStr"/>
-      <c r="L183" s="1" t="inlineStr"/>
-      <c r="M183" s="1" t="inlineStr"/>
-      <c r="N183" s="1" t="inlineStr"/>
-      <c r="O183" s="1" t="inlineStr"/>
-      <c r="P183" s="1" t="inlineStr"/>
-      <c r="Q183" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R183" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '08', 'closes': '23:30'}, 'venerdì': {'opens': '08', 'clos</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="inlineStr">
+      <c r="A184" t="inlineStr">
         <is>
           <t>Trapizzino</t>
         </is>
       </c>
-      <c r="B184" s="1" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Ripa di Porta Ticinese, 2</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>02/91570928</t>
         </is>
       </c>
-      <c r="D184" s="1" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>www.trapizzino.it</t>
         </is>
       </c>
-      <c r="E184" s="1" t="inlineStr">
+      <c r="E184" t="inlineStr">
         <is>
           <t>trapizzino</t>
         </is>
       </c>
-      <c r="F184" s="1" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>trapizzino</t>
         </is>
       </c>
-      <c r="G184" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H184" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I184" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J184" s="1" t="inlineStr"/>
-      <c r="K184" s="1" t="inlineStr"/>
-      <c r="L184" s="1" t="inlineStr"/>
-      <c r="M184" s="1" t="inlineStr"/>
-      <c r="N184" s="1" t="inlineStr"/>
-      <c r="O184" s="1" t="inlineStr"/>
-      <c r="P184" s="1" t="inlineStr"/>
-      <c r="Q184" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R184" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (trapizzino) | IG: trovato (trapizzino)</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -10427,88 +10427,144 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="inlineStr">
-        <is>
-          <t>Coffee Studio 7gr.</t>
-        </is>
-      </c>
-      <c r="B168" s="1" t="inlineStr">
-        <is>
-          <t>Corso Venezia, 31</t>
-        </is>
-      </c>
-      <c r="C168" s="1" t="inlineStr">
-        <is>
-          <t>02/38238682</t>
-        </is>
-      </c>
-      <c r="D168" s="1" t="inlineStr"/>
-      <c r="E168" s="1" t="inlineStr"/>
-      <c r="F168" s="1" t="inlineStr"/>
-      <c r="G168" s="1" t="inlineStr"/>
-      <c r="H168" s="1" t="inlineStr"/>
-      <c r="I168" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J168" s="1" t="inlineStr"/>
-      <c r="K168" s="1" t="inlineStr"/>
-      <c r="L168" s="1" t="inlineStr"/>
-      <c r="M168" s="1" t="inlineStr"/>
-      <c r="N168" s="1" t="inlineStr"/>
-      <c r="O168" s="1" t="inlineStr"/>
-      <c r="P168" s="1" t="inlineStr"/>
-      <c r="Q168" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R168" s="1" t="inlineStr">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Gelato Giusto</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Via San Gregorio, 17</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>02/29510284</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>www.gelatogiusto.it</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>gelatogiustomi</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>gelatogiusto</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '23'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (gelatogiustomi) | IG: trovato (gelatogiusto)</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="inlineStr">
-        <is>
-          <t>Barba</t>
-        </is>
-      </c>
-      <c r="B169" s="1" t="inlineStr">
-        <is>
-          <t>Via San Gregorio, 40</t>
-        </is>
-      </c>
-      <c r="C169" s="1" t="inlineStr">
-        <is>
-          <t>02/36515846</t>
-        </is>
-      </c>
-      <c r="D169" s="1" t="inlineStr"/>
-      <c r="E169" s="1" t="inlineStr"/>
-      <c r="F169" s="1" t="inlineStr"/>
-      <c r="G169" s="1" t="inlineStr"/>
-      <c r="H169" s="1" t="inlineStr"/>
-      <c r="I169" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J169" s="1" t="inlineStr"/>
-      <c r="K169" s="1" t="inlineStr"/>
-      <c r="L169" s="1" t="inlineStr"/>
-      <c r="M169" s="1" t="inlineStr"/>
-      <c r="N169" s="1" t="inlineStr"/>
-      <c r="O169" s="1" t="inlineStr"/>
-      <c r="P169" s="1" t="inlineStr"/>
-      <c r="Q169" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R169" s="1" t="inlineStr">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>GnomoGelato</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Via Francesco Cherubini, 3</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>02/4818134</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>www.lognomogelato.it</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>gnomogelato</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>gnomogelato</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '23'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (gnomogelato) | IG: trovato (gnomogelato)</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -10517,32 +10573,32 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Gelato Giusto</t>
+          <t>Gusto 17</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Via San Gregorio, 17</t>
+          <t>Via Savona, 17</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>02/29510284</t>
+          <t>02/39811835</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>www.gelatogiusto.it</t>
+          <t>www.gusto17.com</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>gelatogiustomi</t>
+          <t>gusto17ilgelato</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>gelatogiusto</t>
+          <t>gusto17_ilgelato</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -10560,16 +10616,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12', 'closes': '23'}, 'venerdì': {'opens': '12', 'closes'</t>
-        </is>
-      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>Si</t>
@@ -10577,7 +10623,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (gelatogiustomi) | IG: trovato (gelatogiusto)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gusto17ilgelato) | IG: trovato (gusto17_ilgelato)</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -10589,32 +10635,32 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GnomoGelato</t>
+          <t>Il Massimo del Gelato</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Via Francesco Cherubini, 3</t>
+          <t>Via Lodovico Castelvetro, 18</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>02/4818134</t>
+          <t>02/3494943</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>www.lognomogelato.it</t>
+          <t>www.ilmassimodelgelato.it</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>gnomogelato</t>
+          <t>ilmassimodelgelatomilano</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>gnomogelato</t>
+          <t>massimodelgelato</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -10649,7 +10695,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (gnomogelato) | IG: trovato (gnomogelato)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (ilmassimodelgelatomilano) | IG: trovato (massimodelgelato)</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -10661,32 +10707,32 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Gusto 17</t>
+          <t>La Bottega del Gelato Cardelli dal 1964</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Via Savona, 17</t>
+          <t>Via Giovanni Battista Pergolesi, 3</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>02/39811835</t>
+          <t>02/2940 0076</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>www.gusto17.com</t>
+          <t>www.labottegadelgelato.it</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>gusto17ilgelato</t>
+          <t>labottegadelgelatocardelli</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>gusto17_ilgelato</t>
+          <t>labottegadelgelatocardelli</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10704,6 +10750,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '10:30', 'closes': '23'}, 'venerdì': {'opens': '10:30', 'c</t>
+        </is>
+      </c>
       <c r="O172" t="inlineStr">
         <is>
           <t>Si</t>
@@ -10711,7 +10767,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gusto17ilgelato) | IG: trovato (gusto17_ilgelato)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (labottegadelgelatocardelli) | IG: trovato (labottegadelgelatocardelli)</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -10723,32 +10779,32 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Il Massimo del Gelato</t>
+          <t>La Gelateria della Musica</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Via Lodovico Castelvetro, 18</t>
+          <t>Via Lodovico il Moro, 3</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>02/3494943</t>
+          <t>02/39288619</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>www.ilmassimodelgelato.it</t>
+          <t>www.lagelateriadellamusica.it</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>ilmassimodelgelatomilano</t>
+          <t>lagelateriadellamusica</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>massimodelgelato</t>
+          <t>lagelateriadellamusica</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -10773,7 +10829,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12', 'closes': '23'}, 'venerdì': {'opens': '12', 'closes'</t>
+          <t>{'giovedì': {'opens': '13:30', 'closes': '22:30'}, 'venerdì': {'opens': '13:30',</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -10783,7 +10839,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (ilmassimodelgelatomilano) | IG: trovato (massimodelgelato)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (lagelateriadellamusica) | IG: trovato (lagelateriadellamusica)</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -10795,32 +10851,27 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>La Bottega del Gelato Cardelli dal 1964</t>
+          <t>Macelleria Popolare</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Via Giovanni Battista Pergolesi, 3</t>
+          <t>Piazza XXIV Maggio - Mercato Coperto</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>02/2940 0076</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>www.labottegadelgelato.it</t>
+          <t>02/39468368</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>labottegadelgelatocardelli</t>
+          <t>mangiaridistradaalmercato</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>labottegadelgelatocardelli</t>
+          <t>noi_della_macelleriapopolare</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10845,7 +10896,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '10:30', 'closes': '23'}, 'venerdì': {'opens': '10:30', 'c</t>
+          <t>{'giovedì': {'opens': '10', 'closes': '21:30'}, 'venerdì': {'opens': '10', 'clos</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -10855,7 +10906,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (labottegadelgelatocardelli) | IG: trovato (labottegadelgelatocardelli)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (mangiaridistradaalmercato) | IG: trovato (noi_della_macelleriapopolare)</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -10867,32 +10918,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>La Gelateria della Musica</t>
+          <t>Out of the Box</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Via Lodovico il Moro, 3</t>
+          <t>Via Marcello Malpighi, 7</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>02/39288619</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>www.lagelateriadellamusica.it</t>
+          <t>02/36637300</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>lagelateriadellamusica</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>lagelateriadellamusica</t>
+          <t>outofthebox.gelato</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -10900,11 +10941,6 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I175" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -10917,7 +10953,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '13:30', 'closes': '22:30'}, 'venerdì': {'opens': '13:30',</t>
+          <t>{'giovedì': {'opens': '12', 'closes': '00'}, 'venerdì': {'opens': '12', 'closes'</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -10927,7 +10963,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (lagelateriadellamusica) | IG: trovato (lagelateriadellamusica)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (outofthebox.gelato) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -10939,7 +10975,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Macelleria Popolare</t>
+          <t>Pantera Pizza Rustica</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10949,27 +10985,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>02/39468368</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>mangiaridistradaalmercato</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>noi_della_macelleriapopolare</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10982,66 +10998,74 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '10', 'closes': '21:30'}, 'venerdì': {'opens': '10', 'clos</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr">
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Pavè Gelati&amp;Granite</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Via Cesare Battisti, 21</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>02/94383619</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>www.pavemilano.com</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>pavemilano</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>pavemilano</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (mangiaridistradaalmercato) | IG: trovato (noi_della_macelleriapopolare)</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="1" t="inlineStr">
-        <is>
-          <t>Orto Gelato</t>
-        </is>
-      </c>
-      <c r="B177" s="1" t="inlineStr">
-        <is>
-          <t>Via Salvatore Pianell, 45</t>
-        </is>
-      </c>
-      <c r="C177" s="1" t="inlineStr">
-        <is>
-          <t>02/09954588</t>
-        </is>
-      </c>
-      <c r="D177" s="1" t="inlineStr"/>
-      <c r="E177" s="1" t="inlineStr"/>
-      <c r="F177" s="1" t="inlineStr"/>
-      <c r="G177" s="1" t="inlineStr"/>
-      <c r="H177" s="1" t="inlineStr"/>
-      <c r="I177" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J177" s="1" t="inlineStr"/>
-      <c r="K177" s="1" t="inlineStr"/>
-      <c r="L177" s="1" t="inlineStr"/>
-      <c r="M177" s="1" t="inlineStr"/>
-      <c r="N177" s="1" t="inlineStr"/>
-      <c r="O177" s="1" t="inlineStr"/>
-      <c r="P177" s="1" t="inlineStr"/>
-      <c r="Q177" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R177" s="1" t="inlineStr">
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (pavemilano) | IG: trovato (pavemilano)</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -11050,22 +11074,32 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Out of the Box</t>
+          <t>Rigoletto</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Via Marcello Malpighi, 7</t>
+          <t>Via Cola di Rienzo, 2</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>02/36637300</t>
+          <t>02/38239075</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>www.gelateriarigoletto.it</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>outofthebox.gelato</t>
+          <t>gelateriarigoletto.it</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>gelateriarigoletto</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -11073,6 +11107,11 @@
           <t>N/D</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -11083,11 +11122,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12', 'closes': '00'}, 'venerdì': {'opens': '12', 'closes'</t>
-        </is>
-      </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>Si</t>
@@ -11095,7 +11129,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (outofthebox.gelato) | IG: nessun handle</t>
+          <t>TF: non trovato | FB: trovato (gelateriarigoletto.it) | IG: trovato (gelateriarigoletto)</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -11107,17 +11141,42 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Pantera Pizza Rustica</t>
+          <t>Terra Gelato</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Piazza XXIV Maggio - Mercato Coperto</t>
+          <t>Via Vitruvio, 38</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>02/91948458</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>www.terragelato.it</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>TerraGelato</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>terragelato</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11125,14 +11184,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>2026</t>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (TerraGelato) | IG: trovato (terragelato)</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -11144,42 +11203,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Pavè Gelati&amp;Granite</t>
+          <t>Tra le righe Gelato &amp; Friends</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Via Cesare Battisti, 21</t>
+          <t>Via Teodosio, 44</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>02/94383619</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>www.pavemilano.com</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>pavemilano</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>pavemilano</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>02/91762549</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11187,14 +11221,19 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '08', 'closes': '23:30'}, 'venerdì': {'opens': '08', 'clos</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (pavemilano) | IG: trovato (pavemilano)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -11206,32 +11245,32 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Rigoletto</t>
+          <t>Trapizzino</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Via Cola di Rienzo, 2</t>
+          <t>Ripa di Porta Ticinese, 2</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>02/38239075</t>
+          <t>02/91570928</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>www.gelateriarigoletto.it</t>
+          <t>www.trapizzino.it</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>gelateriarigoletto.it</t>
+          <t>trapizzino</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>gelateriarigoletto</t>
+          <t>trapizzino</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -11249,190 +11288,163 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (trapizzino) | IG: trovato (trapizzino)</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>Coffee Studio 7gr.</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>Corso Venezia, 31</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>02/38238682</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="inlineStr"/>
+      <c r="E182" s="1" t="inlineStr"/>
+      <c r="F182" s="1" t="inlineStr"/>
+      <c r="G182" s="1" t="inlineStr"/>
+      <c r="H182" s="1" t="inlineStr"/>
+      <c r="I182" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J182" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (gelateriarigoletto.it) | IG: trovato (gelateriarigoletto)</t>
-        </is>
-      </c>
-      <c r="R181" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Terra Gelato</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Via Vitruvio, 38</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>02/91948458</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>www.terragelato.it</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>TerraGelato</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>terragelato</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (TerraGelato) | IG: trovato (terragelato)</t>
-        </is>
-      </c>
-      <c r="R182" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K182" s="1" t="inlineStr"/>
+      <c r="L182" s="1" t="inlineStr"/>
+      <c r="M182" s="1" t="inlineStr"/>
+      <c r="N182" s="1" t="inlineStr"/>
+      <c r="O182" s="1" t="inlineStr"/>
+      <c r="P182" s="1" t="inlineStr"/>
+      <c r="Q182" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R182" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Tra le righe Gelato &amp; Friends</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Via Teodosio, 44</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>02/91762549</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t>Via San Gregorio, 40</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>02/36515846</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="inlineStr"/>
+      <c r="E183" s="1" t="inlineStr"/>
+      <c r="F183" s="1" t="inlineStr"/>
+      <c r="G183" s="1" t="inlineStr"/>
+      <c r="H183" s="1" t="inlineStr"/>
+      <c r="I183" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J183" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '08', 'closes': '23:30'}, 'venerdì': {'opens': '08', 'clos</t>
-        </is>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K183" s="1" t="inlineStr"/>
+      <c r="L183" s="1" t="inlineStr"/>
+      <c r="M183" s="1" t="inlineStr"/>
+      <c r="N183" s="1" t="inlineStr"/>
+      <c r="O183" s="1" t="inlineStr"/>
+      <c r="P183" s="1" t="inlineStr"/>
+      <c r="Q183" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R183" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Trapizzino</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Ripa di Porta Ticinese, 2</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>02/91570928</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>www.trapizzino.it</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>trapizzino</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>trapizzino</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (trapizzino) | IG: trovato (trapizzino)</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>Orto Gelato</t>
+        </is>
+      </c>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t>Via Salvatore Pianell, 45</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>02/09954588</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="inlineStr"/>
+      <c r="E184" s="1" t="inlineStr"/>
+      <c r="F184" s="1" t="inlineStr"/>
+      <c r="G184" s="1" t="inlineStr"/>
+      <c r="H184" s="1" t="inlineStr"/>
+      <c r="I184" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J184" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K184" s="1" t="inlineStr"/>
+      <c r="L184" s="1" t="inlineStr"/>
+      <c r="M184" s="1" t="inlineStr"/>
+      <c r="N184" s="1" t="inlineStr"/>
+      <c r="O184" s="1" t="inlineStr"/>
+      <c r="P184" s="1" t="inlineStr"/>
+      <c r="Q184" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R184" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11348,7 +11348,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11348,7 +11348,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11348,7 +11348,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11348,7 +11348,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11348,7 +11348,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11348,7 +11348,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11343,12 +11343,12 @@
       <c r="P182" s="1" t="inlineStr"/>
       <c r="Q182" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -11391,12 +11391,12 @@
       <c r="P183" s="1" t="inlineStr"/>
       <c r="Q183" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -11439,12 +11439,12 @@
       <c r="P184" s="1" t="inlineStr"/>
       <c r="Q184" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11348,7 +11348,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11348,7 +11348,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -11396,55 +11396,49 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="inlineStr">
+      <c r="A184" t="inlineStr">
         <is>
           <t>Orto Gelato</t>
         </is>
       </c>
-      <c r="B184" s="1" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Via Salvatore Pianell, 45</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>02/09954588</t>
         </is>
       </c>
-      <c r="D184" s="1" t="inlineStr"/>
-      <c r="E184" s="1" t="inlineStr"/>
-      <c r="F184" s="1" t="inlineStr"/>
-      <c r="G184" s="1" t="inlineStr"/>
-      <c r="H184" s="1" t="inlineStr"/>
-      <c r="I184" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J184" s="1" t="inlineStr">
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K184" s="1" t="inlineStr"/>
-      <c r="L184" s="1" t="inlineStr"/>
-      <c r="M184" s="1" t="inlineStr"/>
-      <c r="N184" s="1" t="inlineStr"/>
-      <c r="O184" s="1" t="inlineStr"/>
-      <c r="P184" s="1" t="inlineStr"/>
-      <c r="Q184" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R184" s="1" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '11', 'closes': '23'}, 'venerdì': {'opens': '11', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11305,48 +11305,42 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="inlineStr">
-        <is>
-          <t>Coffee Studio 7gr.</t>
-        </is>
-      </c>
-      <c r="B182" s="1" t="inlineStr">
-        <is>
-          <t>Corso Venezia, 31</t>
-        </is>
-      </c>
-      <c r="C182" s="1" t="inlineStr">
-        <is>
-          <t>02/38238682</t>
-        </is>
-      </c>
-      <c r="D182" s="1" t="inlineStr"/>
-      <c r="E182" s="1" t="inlineStr"/>
-      <c r="F182" s="1" t="inlineStr"/>
-      <c r="G182" s="1" t="inlineStr"/>
-      <c r="H182" s="1" t="inlineStr"/>
-      <c r="I182" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J182" s="1" t="inlineStr">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Orto Gelato</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Via Salvatore Pianell, 45</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>02/09954588</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K182" s="1" t="inlineStr"/>
-      <c r="L182" s="1" t="inlineStr"/>
-      <c r="M182" s="1" t="inlineStr"/>
-      <c r="N182" s="1" t="inlineStr"/>
-      <c r="O182" s="1" t="inlineStr"/>
-      <c r="P182" s="1" t="inlineStr"/>
-      <c r="Q182" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R182" s="1" t="inlineStr">
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '11', 'closes': '23'}, 'venerdì': {'opens': '11', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
@@ -11355,17 +11349,17 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>Barba</t>
+          <t>Coffee Studio 7gr.</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>Via San Gregorio, 40</t>
+          <t>Corso Venezia, 31</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>02/36515846</t>
+          <t>02/38238682</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr"/>
@@ -11396,49 +11390,55 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Orto Gelato</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Via Salvatore Pianell, 45</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>02/09954588</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t>Via San Gregorio, 40</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>02/36515846</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="inlineStr"/>
+      <c r="E184" s="1" t="inlineStr"/>
+      <c r="F184" s="1" t="inlineStr"/>
+      <c r="G184" s="1" t="inlineStr"/>
+      <c r="H184" s="1" t="inlineStr"/>
+      <c r="I184" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J184" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '11', 'closes': '23'}, 'venerdì': {'opens': '11', 'closes'</t>
-        </is>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
+      <c r="K184" s="1" t="inlineStr"/>
+      <c r="L184" s="1" t="inlineStr"/>
+      <c r="M184" s="1" t="inlineStr"/>
+      <c r="N184" s="1" t="inlineStr"/>
+      <c r="O184" s="1" t="inlineStr"/>
+      <c r="P184" s="1" t="inlineStr"/>
+      <c r="Q184" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R184" s="1" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11385,12 +11385,12 @@
       <c r="P183" s="1" t="inlineStr"/>
       <c r="Q183" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11385,12 +11385,12 @@
       <c r="P183" s="1" t="inlineStr"/>
       <c r="Q183" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11390,7 +11390,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11347,50 +11347,39 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="inlineStr">
+      <c r="A183" t="inlineStr">
         <is>
           <t>Coffee Studio 7gr.</t>
         </is>
       </c>
-      <c r="B183" s="1" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Corso Venezia, 31</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>02/38238682</t>
         </is>
       </c>
-      <c r="D183" s="1" t="inlineStr"/>
-      <c r="E183" s="1" t="inlineStr"/>
-      <c r="F183" s="1" t="inlineStr"/>
-      <c r="G183" s="1" t="inlineStr"/>
-      <c r="H183" s="1" t="inlineStr"/>
-      <c r="I183" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J183" s="1" t="inlineStr">
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K183" s="1" t="inlineStr"/>
-      <c r="L183" s="1" t="inlineStr"/>
-      <c r="M183" s="1" t="inlineStr"/>
-      <c r="N183" s="1" t="inlineStr"/>
-      <c r="O183" s="1" t="inlineStr"/>
-      <c r="P183" s="1" t="inlineStr"/>
-      <c r="Q183" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R183" s="1" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11422,12 +11422,12 @@
       <c r="P184" s="1" t="inlineStr"/>
       <c r="Q184" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
